--- a/Src/Assets/Common/Tables/Tables/Versus.xlsx
+++ b/Src/Assets/Common/Tables/Tables/Versus.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CCA\Src\Assets\Common\Tables\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649A8B01-749B-4614-A571-E2A5C5B4A7A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C820F7-751D-44C9-BA75-D39B09741BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="4110" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Attack_Defend_Counter_2dArray" sheetId="1" r:id="rId1"/>
@@ -74,10 +74,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>nuclearbomb</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>block</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -127,6 +123,10 @@
   </si>
   <si>
     <t>deflect</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nuclear_bomb</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -565,31 +565,31 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>17</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -597,28 +597,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="11" t="s">
-        <v>22</v>
-      </c>
       <c r="I2" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -626,28 +626,28 @@
         <v>1</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -655,28 +655,28 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="11" t="s">
-        <v>22</v>
-      </c>
       <c r="I4" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -684,28 +684,28 @@
         <v>3</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -713,28 +713,28 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -742,28 +742,28 @@
         <v>5</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -771,28 +771,28 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -800,28 +800,28 @@
         <v>7</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -829,57 +829,57 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -887,28 +887,28 @@
         <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.35">
@@ -916,57 +916,57 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
